--- a/docs/design/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ログ参照画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ログ参照画面_V1.0.xlsx
@@ -1353,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1513,22 +1513,80 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-08：ログ保持期間が 1年 → **5年** に延びたため、ログ参照の検索期間上限も5年へ変更（ACSMS-MSG-030-002 の文言も「5年以内」へ）。判定はミリ秒定数ではなく暦で加算する（365日×5 だとうるう年ぶん2日足りず、ちょうど5年の指定が弾かれるため）。あわせて **期間（開始）・期間（終了）とも未来日時を指定できない** ようにした（ACSMS-MSG-030-007 / 030-008 を新設）。未来にログは存在せず 0件が返るだけで、条件の誤りに気付けないため。画面はカレンダー側でも未来日を選択不可にするが、時刻部分は手入力でき API 直叩きもあるのでサーバでも弾く。 エラーコードは範囲超過が `DATE_RANGE_TOO_LONG`、未来日時が **`DATE_RANGE_FUTURE`**（いずれも HTTP 400）。</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="21">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="R2:V2"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1701,7 +1759,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2127,7 +2185,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2695,7 +2753,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>検索期間は1年以内で指定してください。</t>
+          <t>検索期間は5年以内で指定してください。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -2732,7 +2790,7 @@
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t>EXPORT_LIMIT_EXCEEDED</t>
+          <t>DATE_RANGE_FUTURE</t>
         </is>
       </c>
       <c r="K15" s="10" t="n"/>
@@ -2748,7 +2806,7 @@
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="19" t="inlineStr">
         <is>
-          <t>検索結果が5,000件を超えています。条件を絞り込んでください。</t>
+          <t>「開始日」／「終了日」に未来の日時は指定できません。（原因の欄名を文言に含む）</t>
         </is>
       </c>
       <c r="W15" s="10" t="n"/>
@@ -2999,7 +3057,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3201,7 +3259,7 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="19" t="inlineStr">
         <is>
-          <t>現在の検索条件で操作ログをCSV形式で出力する（最大5,000件、超過時は409エラー）</t>
+          <t>**画面に表示中のページ**（一覧と同一の検索条件・並び順・page・per_page）のみをCSV形式で出力する（全件出力ではない）。1ページは per_page（最大100件）に収まるため件数上限・409は不要。</t>
         </is>
       </c>
       <c r="T7" s="10" t="n"/>
@@ -3336,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK122"/>
+  <dimension ref="A1:AK121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3497,7 +3555,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4842,7 +4900,7 @@
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="54" customHeight="1">
       <c r="B37" s="31" t="n">
         <v>3</v>
       </c>
@@ -4893,7 +4951,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>ログ種別（1:ユーザー操作, 2:システム, 3:エラー, 4:ファイルアップロード）</t>
+          <t>ログ種別 ※m_code.code_category='LOG_TYPE'を参照（1:ユーザー操作, 2:システム, 3:エラー, 4:ファイルアップロード）</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4909,7 +4967,7 @@
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>log_type_label</t>
+          <t>log_datetime</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4935,7 +4993,11 @@
       </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr"/>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD HH:mm:ss</t>
+        </is>
+      </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
@@ -4953,7 +5015,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>ログ種別ラベル</t>
+          <t>操作日時</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4969,7 +5031,7 @@
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>log_datetime</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4982,7 +5044,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -4995,18 +5057,14 @@
       </c>
       <c r="R39" s="10" t="n"/>
       <c r="S39" s="11" t="n"/>
-      <c r="T39" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD HH:mm:ss</t>
-        </is>
-      </c>
+      <c r="T39" s="17" t="inlineStr"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -5017,7 +5075,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>操作日時</t>
+          <t>アカウントID</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5033,7 +5091,7 @@
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -5046,7 +5104,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -5077,7 +5135,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>アカウントID</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5093,7 +5151,7 @@
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>account_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5137,7 +5195,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>アカウント名</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5153,7 +5211,7 @@
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>account_name</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5166,7 +5224,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -5197,7 +5255,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>アカウント名</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5213,7 +5271,7 @@
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>gamen_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5226,7 +5284,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -5246,7 +5304,7 @@
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z43" s="10" t="n"/>
@@ -5257,7 +5315,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>画面名</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5273,7 +5331,7 @@
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>gamen_name</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5317,7 +5375,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>画面名</t>
+          <t>操作内容</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5326,14 +5384,14 @@
       <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="11" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="54" customHeight="1">
       <c r="B45" s="31" t="n">
         <v>11</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>result_status</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5346,7 +5404,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -5377,7 +5435,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>操作内容</t>
+          <t>結果ステータス ※m_code.code_category='RESULT_STATUS'を参照（1:成功, 2:失敗, 3:警告）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5388,12 +5446,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>result_status</t>
+          <t>target_id</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5426,7 +5484,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -5437,7 +5495,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>結果ステータス（1:成功, 2:失敗, 3:警告）</t>
+          <t>操作対象ID</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5448,12 +5506,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>result_status_label</t>
+          <t>target_table</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5497,7 +5555,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>結果ステータスラベル</t>
+          <t>操作対象テーブル</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5508,12 +5566,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>target_id</t>
+          <t>after_value</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5526,7 +5584,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5546,7 +5604,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -5557,7 +5615,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>操作対象ID</t>
+          <t>変更後値（JSON、詳細欄に表示）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5568,12 +5626,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="38" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C49" s="39" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>target_table</t>
+          <t>ip_address</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5617,7 +5675,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>操作対象テーブル</t>
+          <t>IPアドレス</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5628,14 +5686,14 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>after_value</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
@@ -5646,7 +5704,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5677,7 +5735,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>変更後値（JSON、詳細欄に表示）</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5688,12 +5746,12 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="39" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C51" s="37" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>ip_address</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5706,7 +5764,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -5737,7 +5795,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>IPアドレス</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5748,14 +5806,14 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
       <c r="E52" s="10" t="n"/>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
@@ -5766,7 +5824,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5797,7 +5855,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>現在ページ番号</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5808,12 +5866,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C53" s="37" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5857,7 +5915,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>1ページの件数</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5868,12 +5926,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C54" s="38" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="C54" s="39" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>total_pages</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -5917,7 +5975,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>現在ページ番号</t>
+          <t>総ページ数</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -5926,191 +5984,70 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C55" s="38" t="n"/>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="11" t="n"/>
-      <c r="Y55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="11" t="n"/>
-      <c r="AF55" s="19" t="inlineStr">
-        <is>
-          <t>1ページの件数</t>
-        </is>
-      </c>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="C56" s="39" t="n"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>total_pages</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="n"/>
-      <c r="F56" s="10" t="n"/>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="10" t="n"/>
-      <c r="L56" s="11" t="n"/>
-      <c r="M56" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N56" s="10" t="n"/>
-      <c r="O56" s="10" t="n"/>
-      <c r="P56" s="11" t="n"/>
-      <c r="Q56" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R56" s="10" t="n"/>
-      <c r="S56" s="11" t="n"/>
-      <c r="T56" s="17" t="inlineStr"/>
-      <c r="U56" s="10" t="n"/>
-      <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
-      <c r="X56" s="11" t="n"/>
-      <c r="Y56" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z56" s="10" t="n"/>
-      <c r="AA56" s="10" t="n"/>
-      <c r="AB56" s="10" t="n"/>
-      <c r="AC56" s="10" t="n"/>
-      <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="11" t="n"/>
-      <c r="AF56" s="19" t="inlineStr">
-        <is>
-          <t>総ページ数</t>
-        </is>
-      </c>
-      <c r="AG56" s="10" t="n"/>
-      <c r="AH56" s="10" t="n"/>
-      <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
-      <c r="AK56" s="11" t="n"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1"/>
-    <row r="58" ht="19.5" customHeight="1">
-      <c r="B58" s="40" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="19" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/log?date_from=2026/04/01%2000:00:00&amp;date_to=2026/04/17%2023:59:59&amp;log_type=1&amp;page=1&amp;per_page=20&amp;sort_by=log_datetime&amp;sort_order=desc</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="10" t="n"/>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
-      <c r="T59" s="10" t="n"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="10" t="n"/>
-      <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="10" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="B61" s="40" t="inlineStr">
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="409" customHeight="1">
-      <c r="C62" s="19" t="inlineStr">
+    <row r="60" ht="409" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
     {
       "log_id": 10500,
       "log_type": 1,
-      "log_type_label": "ユーザー操作",
       "log_datetime": "2026/04/17 14:30:45",
       "account_id": 10,
       "login_id": "ja_honten_001",
@@ -6119,7 +6056,6 @@
       "gamen_name": "単価マスタ登録画面 (ACSMS-SCR-003)",
       "operation": "CREATE",
       "result_status": 1,
-      "result_status_label": "成功",
       "target_id": 50,
       "target_table": "m_tanka",
       "after_value": "{\"tanka_id\":50,\"tanka_code\":\"T050\",\"tanka_name\":\"新単価\"}",
@@ -6128,7 +6064,6 @@
     {
       "log_id": 10499,
       "log_type": 3,
-      "log_type_label": "エラー",
       "log_datetime": "2026/04/17 14:25:10",
       "account_id": 10,
       "login_id": "ja_honten_001",
@@ -6137,7 +6072,6 @@
       "gamen_name": "購読者情報登録画面 (ACSMS-SCR-005)",
       "operation": "CREATE",
       "result_status": 2,
-      "result_status_label": "失敗",
       "target_id": null,
       "target_table": "t_dokusya",
       "after_value": "",
@@ -6153,50 +6087,50 @@
 }</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="10" t="n"/>
-      <c r="L62" s="10" t="n"/>
-      <c r="M62" s="10" t="n"/>
-      <c r="N62" s="10" t="n"/>
-      <c r="O62" s="10" t="n"/>
-      <c r="P62" s="10" t="n"/>
-      <c r="Q62" s="10" t="n"/>
-      <c r="R62" s="10" t="n"/>
-      <c r="S62" s="10" t="n"/>
-      <c r="T62" s="10" t="n"/>
-      <c r="U62" s="10" t="n"/>
-      <c r="V62" s="10" t="n"/>
-      <c r="W62" s="10" t="n"/>
-      <c r="X62" s="10" t="n"/>
-      <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="10" t="n"/>
-      <c r="AA62" s="10" t="n"/>
-      <c r="AB62" s="10" t="n"/>
-      <c r="AC62" s="10" t="n"/>
-      <c r="AD62" s="10" t="n"/>
-      <c r="AE62" s="10" t="n"/>
-      <c r="AF62" s="10" t="n"/>
-      <c r="AG62" s="10" t="n"/>
-      <c r="AH62" s="10" t="n"/>
-      <c r="AI62" s="10" t="n"/>
-      <c r="AJ62" s="10" t="n"/>
-      <c r="AK62" s="11" t="n"/>
-    </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="B64" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="72" customHeight="1">
-      <c r="C65" s="19" t="inlineStr">
+    <row r="63" ht="72" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -6204,50 +6138,50 @@
 }</t>
         </is>
       </c>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n"/>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n"/>
-      <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
-      <c r="T65" s="10" t="n"/>
-      <c r="U65" s="10" t="n"/>
-      <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n"/>
-      <c r="X65" s="10" t="n"/>
-      <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
-      <c r="AA65" s="10" t="n"/>
-      <c r="AB65" s="10" t="n"/>
-      <c r="AC65" s="10" t="n"/>
-      <c r="AD65" s="10" t="n"/>
-      <c r="AE65" s="10" t="n"/>
-      <c r="AF65" s="10" t="n"/>
-      <c r="AG65" s="10" t="n"/>
-      <c r="AH65" s="10" t="n"/>
-      <c r="AI65" s="10" t="n"/>
-      <c r="AJ65" s="10" t="n"/>
-      <c r="AK65" s="11" t="n"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="B67" s="40" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="72" customHeight="1">
-      <c r="C68" s="19" t="inlineStr">
+    <row r="66" ht="72" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -6255,50 +6189,50 @@
 }</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="10" t="n"/>
-      <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
-      <c r="O68" s="10" t="n"/>
-      <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
-      <c r="R68" s="10" t="n"/>
-      <c r="S68" s="10" t="n"/>
-      <c r="T68" s="10" t="n"/>
-      <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-      <c r="AA68" s="10" t="n"/>
-      <c r="AB68" s="10" t="n"/>
-      <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
-      <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
-      <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="10" t="n"/>
-      <c r="AJ68" s="10" t="n"/>
-      <c r="AK68" s="11" t="n"/>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="B70" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Validation Error（期間相関エラー））</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="72" customHeight="1">
-      <c r="C71" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATE_RANGE_INVALID",
@@ -6306,50 +6240,50 @@
 }</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
-    </row>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="B73" s="40" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Validation Error（期間が1年超過））</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="72" customHeight="1">
-      <c r="C74" s="19" t="inlineStr">
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATE_RANGE_TOO_LONG",
@@ -6357,50 +6291,50 @@
 }</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="B76" s="40" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="72" customHeight="1">
-      <c r="C77" s="19" t="inlineStr">
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6408,275 +6342,282 @@
 }</t>
         </is>
       </c>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="79" ht="19.5" customHeight="1"/>
-    <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1"/>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>date_from / date_to：有効な日時形式（YYYY/MM/DD HH:mm:ss）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>date_from &gt; date_to の場合：HTTP 400 (`DATE_RANGE_INVALID`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>date_from / date_to：有効な日時形式（YYYY/MM/DD HH:mm:ss）</t>
+          <t>date_to - date_from &gt; 5年 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)。判定は暦で</t>
         </is>
       </c>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>date_from &gt; date_to の場合：HTTP 400 (`DATE_RANGE_INVALID`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="36" customHeight="1">
+          <t>date_from / date_to が現在日時より後の場合：HTTP 400 (`DATE_RANGE_FUTURE`)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>date_to - date_from &gt; 365日 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)</t>
+          <t>log_type：1〜4 または未指定</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>log_type：1〜4 または未指定</t>
+          <t>account_id：数値型</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>account_id：数値型</t>
+          <t>page：1以上</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>page：1以上</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
+          <t>per_page：1〜100</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="36" customHeight="1">
+          <t>sort_by：許可カラム一覧に含まれるか確認（log_datetime, log_type, result_status）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム一覧に含まれるか確認（log_datetime, log_type, result_status）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="D91" s="41" t="inlineStr">
-        <is>
           <t>sort_order：`asc` または `desc`</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="C91" s="41" t="inlineStr">
+        <is>
+          <t>デフォルト値を設定する（page=1, per_page=20, sort_by=log_datetime, sort_order=desc）</t>
         </is>
       </c>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>デフォルト値を設定する（page=1, per_page=20, sort_by=log_datetime, sort_order=desc）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="C95" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
           <t>権限チェック：`log.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="D98" s="41" t="inlineStr">
+    <row r="97" ht="36" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
         <is>
           <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
         </is>
       </c>
     </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="36" customHeight="1">
+    <row r="100" ht="36" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
       <c r="C101" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="C102" s="41" t="inlineStr">
-        <is>
           <t>DataScope を role_code により適用する：</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="36" customHeight="1">
+    <row r="102" ht="36" customHeight="1">
+      <c r="D102" s="41" t="inlineStr">
+        <is>
+          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全ログを参照可（スコープ絞込なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
       <c r="D103" s="41" t="inlineStr">
         <is>
-          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全ログを参照可（スコープ絞込なし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
+          <t>`CHUOKAI`：`l.ja_id = :user_ja_id`（自中央会JAのログのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
       <c r="D104" s="41" t="inlineStr">
         <is>
-          <t>`CHUOKAI`：`l.ja_id = :user_ja_id`（自中央会JAのログのみ）</t>
+          <t>`JA_HONTEN`：`l.ja_id = :user_ja_id`（自JAのログのみ、管理支店のログを含む）</t>
         </is>
       </c>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="D105" s="41" t="inlineStr">
         <is>
-          <t>`JA_HONTEN`：`l.ja_id = :user_ja_id`（自JAのログのみ、管理支店のログを含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="36" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
-        <is>
           <t>`JA_KANRI_SHITEN`：ログのアカウントが自管理支店に所属するもののみ（`a.kanri_shiten_id = :user_kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>検索条件を追加する：</t>
+        </is>
+      </c>
+    </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
-        <is>
-          <t>検索条件を追加する：</t>
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>date_from 指定時：`l.log_datetime &gt;= :date_from`</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="D108" s="41" t="inlineStr">
         <is>
-          <t>date_from 指定時：`l.log_datetime &gt;= :date_from`</t>
+          <t>date_to 指定時：`l.log_datetime &lt;= :date_to`</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="D109" s="41" t="inlineStr">
         <is>
-          <t>date_to 指定時：`l.log_datetime &lt;= :date_to`</t>
+          <t>log_type 指定時：`l.log_type = :log_type`</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>log_type 指定時：`l.log_type = :log_type`</t>
+          <t>account_id 指定時：`l.account_id = :account_id`</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="D111" s="41" t="inlineStr">
-        <is>
-          <t>account_id 指定時：`l.account_id = :account_id`</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="B112" s="27" t="inlineStr">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="234" customHeight="1">
-      <c r="C113" s="42" t="inlineStr">
+    <row r="112" ht="234" customHeight="1">
+      <c r="C112" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_log l
@@ -6693,50 +6634,50 @@
   AND (:account_id IS NULL OR l.account_id = :account_id)</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="342" customHeight="1">
-      <c r="C115" s="42" t="inlineStr">
+    <row r="114" ht="342" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>SELECT l.log_id, l.log_type, l.log_datetime,
        l.account_id, a.login_id, a.account_name,
@@ -6759,152 +6700,157 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D115" s="10" t="n"/>
-      <c r="E115" s="10" t="n"/>
-      <c r="F115" s="10" t="n"/>
-      <c r="G115" s="10" t="n"/>
-      <c r="H115" s="10" t="n"/>
-      <c r="I115" s="10" t="n"/>
-      <c r="J115" s="10" t="n"/>
-      <c r="K115" s="10" t="n"/>
-      <c r="L115" s="10" t="n"/>
-      <c r="M115" s="10" t="n"/>
-      <c r="N115" s="10" t="n"/>
-      <c r="O115" s="10" t="n"/>
-      <c r="P115" s="10" t="n"/>
-      <c r="Q115" s="10" t="n"/>
-      <c r="R115" s="10" t="n"/>
-      <c r="S115" s="10" t="n"/>
-      <c r="T115" s="10" t="n"/>
-      <c r="U115" s="10" t="n"/>
-      <c r="V115" s="10" t="n"/>
-      <c r="W115" s="10" t="n"/>
-      <c r="X115" s="10" t="n"/>
-      <c r="Y115" s="10" t="n"/>
-      <c r="Z115" s="10" t="n"/>
-      <c r="AA115" s="10" t="n"/>
-      <c r="AB115" s="10" t="n"/>
-      <c r="AC115" s="10" t="n"/>
-      <c r="AD115" s="10" t="n"/>
-      <c r="AE115" s="10" t="n"/>
-      <c r="AF115" s="10" t="n"/>
-      <c r="AG115" s="10" t="n"/>
-      <c r="AH115" s="10" t="n"/>
-      <c r="AI115" s="10" t="n"/>
-      <c r="AJ115" s="10" t="n"/>
-      <c r="AK115" s="11" t="n"/>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="B116" s="27" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="36" customHeight="1">
+    <row r="116" ht="36" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>log_type をラベルにマッピング（1→ユーザー操作, 2→システム, 3→エラー, 4→ファイルアップロード）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
       <c r="C117" s="41" t="inlineStr">
         <is>
-          <t>log_type をラベルにマッピング（1→ユーザー操作, 2→システム, 3→エラー, 4→ファイルアップロード）</t>
+          <t>result_status をラベルにマッピング（1→成功, 2→失敗, 3→警告）</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="C118" s="41" t="inlineStr">
         <is>
-          <t>result_status をラベルにマッピング（1→成功, 2→失敗, 3→警告）</t>
+          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="C119" s="41" t="inlineStr">
         <is>
-          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする。</t>
+          <t>data 配列と meta オブジェクトを含むJSONを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含むJSONを返却する。HTTP 200。</t>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="B121" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="C122" s="41" t="inlineStr">
+      <c r="C121" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="302">
+  <mergeCells count="291">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="T53:X53"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="B70:I70"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="D56:L56"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="T55:X55"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="B73:I73"/>
+    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B114:AK114"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="B74:I74"/>
     <mergeCell ref="C95:AK95"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A78:AK78"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -6912,20 +6858,22 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="A80:AK80"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="M45:P45"/>
+    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="D103:AK103"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="A32:AK32"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C36:C51"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="C101:AK101"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D53:L53"/>
@@ -6933,19 +6881,15 @@
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="B116:AK116"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -6960,12 +6904,11 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="C117:AK117"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="M51:P51"/>
@@ -6974,23 +6917,23 @@
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="B64:I64"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B81:AK81"/>
-    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="D52:L52"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
@@ -6999,10 +6942,11 @@
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C52:L52"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C36:C49"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="D102:AK102"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
@@ -7010,15 +6954,13 @@
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C62:AK62"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C82:AK82"/>
-    <mergeCell ref="C107:AK107"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -7027,23 +6969,20 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="B67:I67"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="M55:P55"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
@@ -7054,14 +6993,10 @@
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="AF56:AK56"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="T56:X56"/>
     <mergeCell ref="D105:AK105"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="C119:AK119"/>
@@ -7074,12 +7009,10 @@
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T36:X36"/>
-    <mergeCell ref="Q55:S55"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="B121:AK121"/>
+    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
@@ -7090,25 +7023,26 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="D106:AK106"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="C97:AK97"/>
-    <mergeCell ref="B112:AK112"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D85:AK85"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
@@ -7116,33 +7050,29 @@
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
-    <mergeCell ref="D50:L50"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="D108:AK108"/>
-    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="D86:AK86"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="D86:AK86"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B100:AK100"/>
     <mergeCell ref="D104:AK104"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
-    <mergeCell ref="C53:C56"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
@@ -7158,7 +7088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK105"/>
+  <dimension ref="A1:AK104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7319,7 +7249,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7428,7 +7358,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -7443,7 +7373,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>現在の検索条件で操作ログをCSV形式で出力する（最大5,000件、超過時は409エラー）</t>
+          <t>**画面に表示中のページ**（一覧と同一の検索条件・並び順・page・per_page）のみをCSV形式で出力する（全件出力ではない）。1ページは per_page（最大100件）に収まるため件数上限・409は不要。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -7832,14 +7762,14 @@
       <c r="B17" s="35" t="n"/>
       <c r="I17" s="36" t="n"/>
       <c r="J17" s="17" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>検索結果が5</t>
+          <t>入力値が不正です</t>
         </is>
       </c>
       <c r="O17" s="10" t="n"/>
@@ -7867,17 +7797,23 @@
       <c r="AK17" s="11" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="35" t="n"/>
-      <c r="I18" s="36" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="26" t="n"/>
       <c r="J18" s="17" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>入力値が不正です</t>
+          <t>システムエラーが発生しました</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -7904,68 +7840,92 @@
       <c r="AJ18" s="10" t="n"/>
       <c r="AK18" s="11" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="19" t="inlineStr">
-        <is>
-          <t>システムエラーが発生しました</t>
-        </is>
-      </c>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1"/>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="19" ht="19.5" customHeight="1"/>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1"/>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="11" t="n"/>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="11" t="n"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="11" t="n"/>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="11" t="n"/>
+      <c r="AC22" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG22" s="10" t="n"/>
+      <c r="AH22" s="10" t="n"/>
+      <c r="AI22" s="10" t="n"/>
+      <c r="AJ22" s="10" t="n"/>
+      <c r="AK22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>date_from</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -7977,48 +7937,40 @@
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="11" t="n"/>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R23" s="10" t="n"/>
       <c r="S23" s="11" t="n"/>
-      <c r="T23" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U23" s="10" t="n"/>
       <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
-      </c>
+      <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="10" t="n"/>
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
-      <c r="AC23" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
-      </c>
+      <c r="AC23" s="17" t="inlineStr"/>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
-      <c r="AF23" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>期間（開始日時）（YYYY/MM/DD HH:mm:ss）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -8029,11 +7981,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>date_from</t>
+          <t>date_to</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -8078,7 +8030,7 @@
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>期間（開始日時）（YYYY/MM/DD HH:mm:ss）</t>
+          <t>期間（終了日時）（YYYY/MM/DD HH:mm:ss）</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -8087,13 +8039,13 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="B25" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>date_to</t>
+          <t>log_type</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -8107,7 +8059,7 @@
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N25" s="10" t="n"/>
@@ -8138,7 +8090,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>期間（終了日時）（YYYY/MM/DD HH:mm:ss）</t>
+          <t>ログ種別（1:ユーザー操作, 2:システム, 3:エラー, 4:ファイルアップロード、未指定=すべて）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -8147,13 +8099,13 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="B26" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>log_type</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -8198,7 +8150,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>ログ種別（1:ユーザー操作, 2:システム, 3:エラー, 4:ファイルアップロード、未指定=すべて）</t>
+          <t>アカウントID（ユーザー絞り込み）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -8209,11 +8161,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -8258,7 +8210,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>アカウントID（ユーザー絞り込み）</t>
+          <t>ページ番号（デフォルト: 1）。表示中ページと一致させる</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -8267,168 +8219,206 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1"/>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="11" t="n"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n"/>
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="11" t="n"/>
+      <c r="Y28" s="17" t="inlineStr"/>
+      <c r="Z28" s="10" t="n"/>
+      <c r="AA28" s="10" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="17" t="inlineStr"/>
+      <c r="AD28" s="10" t="n"/>
+      <c r="AE28" s="11" t="n"/>
+      <c r="AF28" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（デフォルト: 20、最大: 100）</t>
+        </is>
+      </c>
+      <c r="AG28" s="10" t="n"/>
+      <c r="AH28" s="10" t="n"/>
+      <c r="AI28" s="10" t="n"/>
+      <c r="AJ28" s="10" t="n"/>
+      <c r="AK28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="B29" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="17" t="inlineStr"/>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="17" t="inlineStr"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="19" t="inlineStr">
+        <is>
+          <t>並び替えカラム（log_datetime / log_type / result_status、デフォルト: log_datetime）</t>
+        </is>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>並び順（asc / desc、デフォルト: desc）</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1"/>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="10" t="n"/>
-      <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="inlineStr"/>
-      <c r="C32" s="19" t="inlineStr"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>log_id</t>
-        </is>
-      </c>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="31" t="inlineStr"/>
-      <c r="C33" s="19" t="inlineStr"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="17" t="inlineStr"/>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="17" t="inlineStr"/>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="17" t="inlineStr"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="inlineStr"/>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="19" t="inlineStr">
-        <is>
-          <t>log_type_label</t>
-        </is>
-      </c>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="inlineStr"/>
-      <c r="C34" s="19" t="inlineStr"/>
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="10" t="n"/>
       <c r="F34" s="10" t="n"/>
@@ -8438,28 +8428,44 @@
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr"/>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
+      <c r="T34" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr"/>
+      <c r="Y34" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="10" t="n"/>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>log_datetime</t>
+      <c r="AF34" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -8501,7 +8507,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>log_id</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -8510,7 +8516,7 @@
       <c r="AJ35" s="10" t="n"/>
       <c r="AK35" s="11" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="36" customHeight="1">
       <c r="B36" s="31" t="inlineStr"/>
       <c r="C36" s="19" t="inlineStr"/>
       <c r="D36" s="10" t="n"/>
@@ -8543,7 +8549,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>log_type → m_code.label('LOG_TYPE')</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -8585,7 +8591,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>gamen_name</t>
+          <t>log_datetime</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -8627,7 +8633,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -8669,7 +8675,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>result_status_label</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -8711,7 +8717,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>target_id</t>
+          <t>gamen_name</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -8753,7 +8759,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>target_table</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -8762,7 +8768,7 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="inlineStr"/>
       <c r="C42" s="19" t="inlineStr"/>
       <c r="D42" s="10" t="n"/>
@@ -8795,7 +8801,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>ip_address</t>
+          <t>result_status → m_code.label('RESULT_STATUS')</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -8804,20 +8810,93 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="19.5" customHeight="1"/>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="31" t="inlineStr"/>
+      <c r="C43" s="19" t="inlineStr"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="17" t="inlineStr"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="17" t="inlineStr"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="17" t="inlineStr"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="17" t="inlineStr"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="19" t="inlineStr">
+        <is>
+          <t>target_id</t>
+        </is>
+      </c>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="31" t="inlineStr"/>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="17" t="inlineStr"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="11" t="n"/>
+      <c r="Q44" s="17" t="inlineStr"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="11" t="n"/>
+      <c r="T44" s="17" t="inlineStr"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="11" t="n"/>
+      <c r="Y44" s="17" t="inlineStr"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="19" t="inlineStr">
+        <is>
+          <t>target_table</t>
+        </is>
+      </c>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/log/export?date_from=2026/04/01%2000:00:00&amp;date_to=2026/04/17%2023:59:59&amp;log_type=1</t>
-        </is>
-      </c>
+      <c r="B45" s="31" t="inlineStr"/>
+      <c r="C45" s="19" t="inlineStr"/>
       <c r="D45" s="10" t="n"/>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
@@ -8826,46 +8905,49 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="17" t="inlineStr"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="10" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="17" t="inlineStr"/>
       <c r="R45" s="10" t="n"/>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="10" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="17" t="inlineStr"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
-      <c r="X45" s="10" t="n"/>
-      <c r="Y45" s="10" t="n"/>
+      <c r="X45" s="11" t="n"/>
+      <c r="Y45" s="17" t="inlineStr"/>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="10" t="n"/>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="10" t="n"/>
-      <c r="AF45" s="10" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="19" t="inlineStr">
+        <is>
+          <t>ip_address</t>
+        </is>
+      </c>
       <c r="AG45" s="10" t="n"/>
       <c r="AH45" s="10" t="n"/>
       <c r="AI45" s="10" t="n"/>
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
+    <row r="46" ht="19.5" customHeight="1"/>
     <row r="47" ht="19.5" customHeight="1">
       <c r="B47" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="54" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>"ログID","ログ種別","日時","ユーザーID","JA ID","画面名","操作内容","結果","対象ID","対象テーブル","IPアドレス"
-"10500","ユーザー操作","2026/04/17 14:30:45","ja_honten_001","100","単価マスタ登録画面 (ACSMS-SCR-003)","CREATE","成功","50","m_tanka","192.168.1.100"
-"10499","エラー","2026/04/17 14:25:10","ja_honten_001","100","購読者情報登録画面 (ACSMS-SCR-005)","CREATE","失敗","","t_dokusya","192.168.1.100"</t>
+          <t>GET /api/v1/log/export?date_from=2026/04/01%2000:00:00&amp;date_to=2026/04/17%2023:59:59&amp;log_type=1</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -8906,17 +8988,16 @@
     <row r="50" ht="19.5" customHeight="1">
       <c r="B50" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="72" customHeight="1">
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
-}</t>
+          <t>"ログID","ログ種別","日時","ユーザーID","JA ID","画面名","操作内容","結果","対象ID","対象テーブル","IPアドレス"
+"10500","ユーザー操作","2026/04/17 14:30:45","ja_honten_001","100","単価マスタ登録画面 (ACSMS-SCR-003)","CREATE","成功","50","m_tanka","192.168.1.100"
+"10499","エラー","2026/04/17 14:25:10","ja_honten_001","100","購読者情報登録画面 (ACSMS-SCR-005)","CREATE","失敗","","t_dokusya","192.168.1.100"</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -8957,7 +9038,7 @@
     <row r="53" ht="19.5" customHeight="1">
       <c r="B53" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -8965,8 +9046,8 @@
       <c r="C54" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
 }</t>
         </is>
       </c>
@@ -9008,7 +9089,7 @@
     <row r="56" ht="19.5" customHeight="1">
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 409 Conflict（件数超過））</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -9016,8 +9097,8 @@
       <c r="C57" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "EXPORT_LIMIT_EXCEEDED",
-  "message": "検索結果が5,000件を超えています。条件を絞り込んでください"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
 }</t>
         </is>
       </c>
@@ -9197,159 +9278,106 @@
     <row r="71" ht="36" customHeight="1">
       <c r="D71" s="41" t="inlineStr">
         <is>
-          <t>date_to - date_from &gt; 365日 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
+          <t>date_to - date_from &gt; 5年 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)。判定は暦で</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
       <c r="D72" s="41" t="inlineStr">
         <is>
-          <t>log_type：1〜4 または未指定</t>
+          <t>date_from / date_to が現在日時より後の場合：HTTP 400 (`DATE_RANGE_FUTURE`)。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
+          <t>log_type：1〜4 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="D74" s="41" t="inlineStr">
+        <is>
           <t>account_id：数値型</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="36" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
+    <row r="75" ht="36" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="27" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="C77" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="C78" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
           <t>権限チェック：`log.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
+    <row r="80" ht="36" customHeight="1">
+      <c r="D80" s="41" t="inlineStr">
         <is>
           <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ件数チェック（5,000件上限）</t>
-        </is>
-      </c>
-    </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>検索条件で対象件数を先にカウントする（DataScope適用）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="234" customHeight="1">
-      <c r="C83" s="42" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*)
-FROM t_log l
-LEFT JOIN m_account a ON a.account_id = l.account_id AND a.deleted_at IS NULL
-WHERE 1 = 1
-  /* DataScope: CHUOKAI / JA_HONTEN */
-  AND l.ja_id = :user_ja_id
-  /* DataScope: JA_KANRI_SHITEN */
-  AND a.kanri_shiten_id = :user_kanri_shiten_id
-  /* 検索条件 */
-  AND (:date_from IS NULL OR l.log_datetime &gt;= :date_from)
-  AND (:date_to IS NULL OR l.log_datetime &lt;= :date_to)
-  AND (:log_type IS NULL OR l.log_type = :log_type)
-  AND (:account_id IS NULL OR l.account_id = :account_id)</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="36" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得（表示中ページのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>一覧 (API-030-001) と同一の検索条件・DataScope・並び順で、**現在ページのみ**を</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
       <c r="C84" s="41" t="inlineStr">
         <is>
-          <t>件数が 5,000 を超える場合：HTTP 409 (`EXPORT_LIMIT_EXCEEDED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="342" customHeight="1">
-      <c r="C86" s="42" t="inlineStr">
+          <t>1ページは per_page（最大100）に収まるため、件数上限チェック・409は行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="342" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
         <is>
           <t>SELECT l.log_id, l.log_type, l.log_datetime,
-       l.account_id, a.login_id,
+       a.login_id,
        l.ja_id, l.gamen_name, l.operation,
        l.result_status, l.target_id, l.target_table,
        l.ip_address
@@ -9365,110 +9393,110 @@
   AND (:date_to IS NULL OR l.log_datetime &lt;= :date_to)
   AND (:log_type IS NULL OR l.log_type = :log_type)
   AND (:account_id IS NULL OR l.account_id = :account_id)
-ORDER BY l.log_datetime DESC
-LIMIT 5000</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="10" t="n"/>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="10" t="n"/>
-      <c r="R86" s="10" t="n"/>
-      <c r="S86" s="10" t="n"/>
-      <c r="T86" s="10" t="n"/>
-      <c r="U86" s="10" t="n"/>
-      <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="10" t="n"/>
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-      <c r="AA86" s="10" t="n"/>
-      <c r="AB86" s="10" t="n"/>
-      <c r="AC86" s="10" t="n"/>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="10" t="n"/>
-      <c r="AF86" s="10" t="n"/>
-      <c r="AG86" s="10" t="n"/>
-      <c r="AH86" s="10" t="n"/>
-      <c r="AI86" s="10" t="n"/>
-      <c r="AJ86" s="10" t="n"/>
-      <c r="AK86" s="11" t="n"/>
+ORDER BY :sort_by :sort_order
+LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>4.5 CSV生成</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
-        <is>
-          <t>4.5 CSV生成</t>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>ファイル名：`log_export_YYYYMMDD_HHmmss.csv`（現在日時）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>ファイル名：`log_export_YYYYMMDD_HHmmss.csv`（現在日時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
+          <t>文字コード：UTF-8 with BOM（日本語Excel対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>文字コード：UTF-8 with BOM（日本語Excel対応）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="36" customHeight="1">
+          <t>ヘッダー行：`ログID, ログ種別, 日時, ユーザーID, JA ID, 画面名, 操作内容, 結果, 対象ID, 対象テーブル, IPアドレス`</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>ヘッダー行：`ログID, ログ種別, 日時, ユーザーID, JA ID, 画面名, 操作内容, 結果, 対象ID, 対象テーブル, IPアドレス`</t>
+          <t>log_type をラベルにマッピング（1→ユーザー操作 等）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>log_type をラベルにマッピング（1→ユーザー操作 等）</t>
+          <t>result_status をラベルにマッピング（1→成功 等）</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>result_status をラベルにマッピング（1→成功 等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
+          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
       <c r="C93" s="41" t="inlineStr">
         <is>
-          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
           <t>CSV escape：値に `,`、`"`、改行を含む場合はダブルクォートで囲み `"` は `""` にエスケープする</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="216" customHeight="1">
-      <c r="C96" s="42" t="inlineStr">
+    <row r="95" ht="216" customHeight="1">
+      <c r="C95" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9482,6 +9510,55 @@
         '', :after_value_json,
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="10" t="n"/>
+      <c r="X95" s="10" t="n"/>
+      <c r="Y95" s="10" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="11" t="n"/>
+    </row>
+    <row r="96" ht="180" customHeight="1">
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：EXPORT のため空文字列を設定する。
+`after_value`：エクスポート条件と件数をJSON形式で格納する。
+{
+  "date_from": "2026/04/01 00:00:00",
+  "date_to": "2026/04/17 23:59:59",
+  "log_type": 1,
+  "account_id": null,
+  "record_count": 250
+}</t>
         </is>
       </c>
       <c r="D96" s="10" t="n"/>
@@ -9519,106 +9596,57 @@
       <c r="AJ96" s="10" t="n"/>
       <c r="AK96" s="11" t="n"/>
     </row>
-    <row r="97" ht="180" customHeight="1">
-      <c r="C97" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：EXPORT のため空文字列を設定する。
-`after_value`：エクスポート条件と件数をJSON形式で格納する。
-{
-  "date_from": "2026/04/01 00:00:00",
-  "date_to": "2026/04/17 23:59:59",
-  "log_type": 1,
-  "account_id": null,
-  "record_count": 250
-}</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>4.7 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="B98" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>CSV ファイルをレスポンスボディとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>CSV ファイルをレスポンスボディとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
+          <t>`Content-Type: text/csv; charset=utf-8`</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
       <c r="C100" s="41" t="inlineStr">
         <is>
-          <t>`Content-Type: text/csv; charset=utf-8`</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
-        <is>
           <t>`Content-Disposition: attachment; filename="log_export_YYYYMMDD_HHmmss.csv"`</t>
         </is>
       </c>
     </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>4.8 例外処理</t>
+        </is>
+      </c>
+    </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
-        <is>
-          <t>4.8 例外処理</t>
+      <c r="C102" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="216" customHeight="1">
-      <c r="C105" s="42" t="inlineStr">
+    <row r="104" ht="216" customHeight="1">
+      <c r="C104" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9634,59 +9662,59 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="10" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="10" t="n"/>
+      <c r="J104" s="10" t="n"/>
+      <c r="K104" s="10" t="n"/>
+      <c r="L104" s="10" t="n"/>
+      <c r="M104" s="10" t="n"/>
+      <c r="N104" s="10" t="n"/>
+      <c r="O104" s="10" t="n"/>
+      <c r="P104" s="10" t="n"/>
+      <c r="Q104" s="10" t="n"/>
+      <c r="R104" s="10" t="n"/>
+      <c r="S104" s="10" t="n"/>
+      <c r="T104" s="10" t="n"/>
+      <c r="U104" s="10" t="n"/>
+      <c r="V104" s="10" t="n"/>
+      <c r="W104" s="10" t="n"/>
+      <c r="X104" s="10" t="n"/>
+      <c r="Y104" s="10" t="n"/>
+      <c r="Z104" s="10" t="n"/>
+      <c r="AA104" s="10" t="n"/>
+      <c r="AB104" s="10" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="10" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="10" t="n"/>
+      <c r="AK104" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="228">
     <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="B62:I62"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="T33:X33"/>
+    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D71:AK71"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M32:P32"/>
     <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="C68:AK68"/>
@@ -9695,78 +9723,82 @@
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D73:AK73"/>
-    <mergeCell ref="C45:AK45"/>
+    <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N19:AK19"/>
-    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C91:AK91"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C84:AK84"/>
-    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="C51:AK51"/>
-    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="C95:AK95"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="C48:AK48"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="M33:P33"/>
-    <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="M45:P45"/>
+    <mergeCell ref="T30:X30"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="B47:I47"/>
     <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="A32:AK32"/>
+    <mergeCell ref="T38:X38"/>
     <mergeCell ref="B59:I59"/>
-    <mergeCell ref="T38:X38"/>
-    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B67:AK67"/>
-    <mergeCell ref="Y33:AE33"/>
+    <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B101:AK101"/>
+    <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="C88:AK88"/>
-    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="C35:L35"/>
-    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="C25:L25"/>
@@ -9774,42 +9806,50 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="A66:AK66"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="M37:P37"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="C96:AK96"/>
     <mergeCell ref="C78:AK78"/>
-    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="C37:L37"/>
-    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="A29:AK29"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="C54:AK54"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="C63:AK63"/>
@@ -9817,21 +9857,27 @@
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
-    <mergeCell ref="M31:P31"/>
     <mergeCell ref="M40:P40"/>
+    <mergeCell ref="T43:X43"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="C43:L43"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
@@ -9840,7 +9886,6 @@
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="M38:P38"/>
@@ -9848,34 +9893,40 @@
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="B98:AK98"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="D74:AK74"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="C97:AK97"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B44:I44"/>
     <mergeCell ref="B53:I53"/>
+    <mergeCell ref="C45:L45"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="D69:AK69"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="B76:AK76"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C44:L44"/>
     <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="B85:AK85"/>
-    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="Q28:S28"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="M22:P22"/>
     <mergeCell ref="C40:L40"/>
-    <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B75:AK75"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="AC30:AE30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10048,7 +10099,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>

--- a/docs/design/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ログ参照画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ログ参照画面_V1.0.xlsx
@@ -1353,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1564,15 +1564,70 @@
       <c r="AF3" s="10" t="n"/>
       <c r="AG3" s="11" t="n"/>
     </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>実装コードとの突合により以下を修正。①ACSMS-API-030-001のレスポンス失敗例が版1.1で「1年」表記のまま未修正だった箇所（見出し・メッセージとも）を「5年」へ修正し、両APIの失敗例に `DATE_RANGE_FUTURE` の例を追加。②ACSMS-API-030-002の処理手順4.5「CSV escape」記述を実装（`log.service.ts` `csvEscape()`）に合わせ、全値を無条件でダブルクォート囲みする仕様、および数式インジェクション対策（`=+-@`／タブ／CRで始まる値の先頭にシングルクォート付与）を追記。ORDER BY疑似SQLの `l.` プレフィックス欠落を修正。③ACSMS-API-COMMON-005（Get Account Dropdown）を全面改訂 — 「リクエストパラメータなし」「レスポンスはdata配列のみ」という記述は commit `3c8a98b7`（ユーザー filter — infinite-scroll dropdown）で追加された `q` / `match_field` / `page` / `per_page` / `include_id` クエリと `meta`（total, page, per_page, has_more）を反映しておらず実装と乖離していたため、リクエストパラメータ表・レスポンスデータ表・成功/失敗例・処理手順を実装（`account.controller.ts` / `account.service.ts` / `account-dropdown-query.dto.ts`）に合わせて書き直した。あわせて、本APIには `@Permissions` が付与されておらず（[shared-dropdown-rule]）実際には403を返さないため、概要表・処理手順4.2から誤った403記載を削除。</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="17" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="17" t="inlineStr"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="28">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="R4:V4"/>
     <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:Q4"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W4:AA4"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
@@ -1583,8 +1638,11 @@
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
+    <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
@@ -1759,7 +1817,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1767,7 +1825,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -2185,7 +2243,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2193,7 +2251,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3057,7 +3115,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3065,7 +3123,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3316,7 +3374,7 @@
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="19" t="inlineStr">
         <is>
-          <t>アカウントプルダウンリストを取得する（DataScopeを呼び出しユーザーのロールに基づき自動適用。共用API）</t>
+          <t>アカウントプルダウンリストを取得する（キーワード検索＋ページング対応の無限スクロール用。DataScopeを呼び出しユーザーのロールに基づき自動適用。共用API）</t>
         </is>
       </c>
       <c r="T8" s="10" t="n"/>
@@ -3394,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3555,7 +3613,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3563,7 +3621,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -6278,7 +6336,7 @@
     <row r="71" ht="19.5" customHeight="1">
       <c r="B71" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Validation Error（期間が1年超過））</t>
+          <t>レスポンス（失敗 400 Validation Error（期間が5年超過））</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6345,7 @@
         <is>
           <t>{
   "error_code": "DATE_RANGE_TOO_LONG",
-  "message": "検索期間は1年以内で指定してください"
+  "message": "検索期間は5年以内で指定してください"
 }</t>
         </is>
       </c>
@@ -6329,7 +6387,7 @@
     <row r="74" ht="19.5" customHeight="1">
       <c r="B74" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 400 Validation Error（未来日時））</t>
         </is>
       </c>
     </row>
@@ -6337,8 +6395,8 @@
       <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "DATE_RANGE_FUTURE",
+  "message": "「開始日」に未来の日時は指定できません"
 }</t>
         </is>
       </c>
@@ -6377,247 +6435,298 @@
       <c r="AJ75" s="10" t="n"/>
       <c r="AK75" s="11" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="B77" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="72" customHeight="1">
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1"/>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>date_from / date_to：有効な日時形式（YYYY/MM/DD HH:mm:ss）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
+    <row r="85" ht="36" customHeight="1">
+      <c r="D85" s="41" t="inlineStr">
         <is>
           <t>date_from &gt; date_to の場合：HTTP 400 (`DATE_RANGE_INVALID`)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
+    <row r="86" ht="36" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
         <is>
           <t>date_to - date_from &gt; 5年 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)。判定は暦で</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
+    <row r="87" ht="36" customHeight="1">
+      <c r="D87" s="41" t="inlineStr">
         <is>
           <t>date_from / date_to が現在日時より後の場合：HTTP 400 (`DATE_RANGE_FUTURE`)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>log_type：1〜4 または未指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>account_id：数値型</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>page：1以上</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="36" customHeight="1">
+          <t>log_type：1〜4 または未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム一覧に含まれるか確認（log_datetime, log_type, result_status）</t>
+          <t>account_id：数値型</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
+          <t>page：1以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可カラム一覧に含まれるか確認（log_datetime, log_type, result_status）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
           <t>sort_order：`asc` または `desc`</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
+    <row r="94" ht="36" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>デフォルト値を設定する（page=1, per_page=20, sort_by=log_datetime, sort_order=desc）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="B93" s="27" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
         <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`log.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="D97" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`log.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="36" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="C101" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
           <t>DataScope を role_code により適用する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="36" customHeight="1">
-      <c r="D102" s="41" t="inlineStr">
-        <is>
-          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全ログを参照可（スコープ絞込なし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="D103" s="41" t="inlineStr">
-        <is>
-          <t>`CHUOKAI`：`l.ja_id = :user_ja_id`（自中央会JAのログのみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="36" customHeight="1">
-      <c r="D104" s="41" t="inlineStr">
-        <is>
-          <t>`JA_HONTEN`：`l.ja_id = :user_ja_id`（自JAのログのみ、管理支店のログを含む）</t>
         </is>
       </c>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="D105" s="41" t="inlineStr">
         <is>
+          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全ログを参照可（スコープ絞込なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>`CHUOKAI`：`l.ja_id = :user_ja_id`（自中央会JAのログのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>`JA_HONTEN`：`l.ja_id = :user_ja_id`（自JAのログのみ、管理支店のログを含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="D108" s="41" t="inlineStr">
+        <is>
           <t>`JA_KANRI_SHITEN`：ログのアカウントが自管理支店に所属するもののみ（`a.kanri_shiten_id = :user_kanri_shiten_id`）</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>検索条件を追加する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>date_from 指定時：`l.log_datetime &gt;= :date_from`</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>date_to 指定時：`l.log_datetime &lt;= :date_to`</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
-        <is>
-          <t>log_type 指定時：`l.log_type = :log_type`</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
+          <t>date_from 指定時：`l.log_datetime &gt;= :date_from`</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>date_to 指定時：`l.log_datetime &lt;= :date_to`</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>log_type 指定時：`l.log_type = :log_type`</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
           <t>account_id 指定時：`l.account_id = :account_id`</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="234" customHeight="1">
-      <c r="C112" s="42" t="inlineStr">
+    <row r="115" ht="234" customHeight="1">
+      <c r="C115" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_log l
@@ -6634,50 +6743,50 @@
   AND (:account_id IS NULL OR l.account_id = :account_id)</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="B113" s="27" t="inlineStr">
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="342" customHeight="1">
-      <c r="C114" s="42" t="inlineStr">
+    <row r="117" ht="342" customHeight="1">
+      <c r="C117" s="42" t="inlineStr">
         <is>
           <t>SELECT l.log_id, l.log_type, l.log_datetime,
        l.account_id, a.login_id, a.account_name,
@@ -6700,92 +6809,93 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="n"/>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="n"/>
-      <c r="O114" s="10" t="n"/>
-      <c r="P114" s="10" t="n"/>
-      <c r="Q114" s="10" t="n"/>
-      <c r="R114" s="10" t="n"/>
-      <c r="S114" s="10" t="n"/>
-      <c r="T114" s="10" t="n"/>
-      <c r="U114" s="10" t="n"/>
-      <c r="V114" s="10" t="n"/>
-      <c r="W114" s="10" t="n"/>
-      <c r="X114" s="10" t="n"/>
-      <c r="Y114" s="10" t="n"/>
-      <c r="Z114" s="10" t="n"/>
-      <c r="AA114" s="10" t="n"/>
-      <c r="AB114" s="10" t="n"/>
-      <c r="AC114" s="10" t="n"/>
-      <c r="AD114" s="10" t="n"/>
-      <c r="AE114" s="10" t="n"/>
-      <c r="AF114" s="10" t="n"/>
-      <c r="AG114" s="10" t="n"/>
-      <c r="AH114" s="10" t="n"/>
-      <c r="AI114" s="10" t="n"/>
-      <c r="AJ114" s="10" t="n"/>
-      <c r="AK114" s="11" t="n"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="B118" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="36" customHeight="1">
-      <c r="C116" s="41" t="inlineStr">
+    <row r="119" ht="36" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
         <is>
           <t>log_type をラベルにマッピング（1→ユーザー操作, 2→システム, 3→エラー, 4→ファイルアップロード）</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="C117" s="41" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="C120" s="41" t="inlineStr">
         <is>
           <t>result_status をラベルにマッピング（1→成功, 2→失敗, 3→警告）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
-        <is>
-          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含むJSONを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="C121" s="41" t="inlineStr">
         <is>
+          <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta オブジェクトを含むJSONを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="C124" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="291">
+  <mergeCells count="293">
+    <mergeCell ref="B102:AK102"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -6811,20 +6921,18 @@
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
+    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
-    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
@@ -6836,8 +6944,6 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
@@ -6850,7 +6956,8 @@
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="C95:AK95"/>
     <mergeCell ref="B68:I68"/>
-    <mergeCell ref="A78:AK78"/>
+    <mergeCell ref="B114:AK114"/>
+    <mergeCell ref="B123:AK123"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -6858,17 +6965,14 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="B93:AK93"/>
-    <mergeCell ref="D103:AK103"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="A32:AK32"/>
     <mergeCell ref="T38:X38"/>
@@ -6882,12 +6986,14 @@
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="B116:AK116"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D89:AK89"/>
     <mergeCell ref="Z2:AC3"/>
@@ -6902,32 +7008,34 @@
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="B118:AK118"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="D90:AK90"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
@@ -6945,8 +7053,7 @@
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="C36:C49"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="D102:AK102"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
@@ -6960,7 +7067,8 @@
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -6969,7 +7077,7 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="A81:AK81"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
@@ -6997,6 +7105,7 @@
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="C119:AK119"/>
@@ -7011,13 +7120,14 @@
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
+    <mergeCell ref="B96:AK96"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
@@ -7026,36 +7136,38 @@
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="B111:AK111"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="B71:I71"/>
-    <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="B120:AK120"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D85:AK85"/>
-    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
+    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
@@ -7067,7 +7179,6 @@
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="D104:AK104"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Y34:AE34"/>
@@ -7088,7 +7199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK104"/>
+  <dimension ref="A1:AK110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7249,7 +7360,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7257,7 +7368,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -9140,7 +9251,7 @@
     <row r="59" ht="19.5" customHeight="1">
       <c r="B59" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Validation Error）</t>
+          <t>レスポンス（失敗 400 Validation Error（期間相関エラー））</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9302,7 @@
     <row r="62" ht="19.5" customHeight="1">
       <c r="B62" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 400 Validation Error（期間が5年超過））</t>
         </is>
       </c>
     </row>
@@ -9199,8 +9310,8 @@
       <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "DATE_RANGE_TOO_LONG",
+  "message": "検索期間は5年以内で指定してください"
 }</t>
         </is>
       </c>
@@ -9239,142 +9350,244 @@
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
-    <row r="65" ht="19.5" customHeight="1"/>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="27" t="inlineStr">
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Validation Error（未来日時））</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="72" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "DATE_RANGE_FUTURE",
+  "message": "「終了日」に未来の日時は指定できません"
+}</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1"/>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="B67" s="27" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="C68" s="41" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="D69" s="41" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="D75" s="41" t="inlineStr">
         <is>
           <t>date_from / date_to：有効な日時形式（YYYY/MM/DD HH:mm:ss）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="D70" s="41" t="inlineStr">
+    <row r="76" ht="36" customHeight="1">
+      <c r="D76" s="41" t="inlineStr">
         <is>
           <t>date_from &gt; date_to の場合：HTTP 400 (`DATE_RANGE_INVALID`)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="D71" s="41" t="inlineStr">
+    <row r="77" ht="36" customHeight="1">
+      <c r="D77" s="41" t="inlineStr">
         <is>
           <t>date_to - date_from &gt; 5年 の場合：HTTP 400 (`DATE_RANGE_TOO_LONG`)。判定は暦で</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="D72" s="41" t="inlineStr">
+    <row r="78" ht="36" customHeight="1">
+      <c r="D78" s="41" t="inlineStr">
         <is>
           <t>date_from / date_to が現在日時より後の場合：HTTP 400 (`DATE_RANGE_FUTURE`)。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="D73" s="41" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
         <is>
           <t>log_type：1〜4 または未指定</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="D74" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="D80" s="41" t="inlineStr">
         <is>
           <t>account_id：数値型</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
+    <row r="81" ht="36" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`) または HTTP 400 (`VALIDATION_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="B76" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`log.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>4.3 データ取得（表示中ページのみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>一覧 (API-030-001) と同一の検索条件・DataScope・並び順で、**現在ページのみ**を</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="C84" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`log.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN, NICHINO_STAFF, CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN（全ロール保持）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得（表示中ページのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>一覧 (API-030-001) と同一の検索条件・DataScope・並び順で、**現在ページのみ**を</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
           <t>1ページは per_page（最大100）に収まるため、件数上限チェック・409は行わない。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="342" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="91" ht="342" customHeight="1">
+      <c r="C91" s="42" t="inlineStr">
         <is>
           <t>SELECT l.log_id, l.log_type, l.log_datetime,
        a.login_id,
@@ -9393,110 +9606,110 @@
   AND (:date_to IS NULL OR l.log_datetime &lt;= :date_to)
   AND (:log_type IS NULL OR l.log_type = :log_type)
   AND (:account_id IS NULL OR l.account_id = :account_id)
-ORDER BY :sort_by :sort_order
+ORDER BY l.:sort_by :sort_order
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="B86" s="27" t="inlineStr">
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>4.5 CSV生成</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
         <is>
           <t>ファイル名：`log_export_YYYYMMDD_HHmmss.csv`（現在日時）</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>文字コード：UTF-8 with BOM（日本語Excel対応）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="36" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>ヘッダー行：`ログID, ログ種別, 日時, ユーザーID, JA ID, 画面名, 操作内容, 結果, 対象ID, 対象テーブル, IPアドレス`</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>log_type をラベルにマッピング（1→ユーザー操作 等）</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
         <is>
           <t>result_status をラベルにマッピング（1→成功 等）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>log_datetime を `YYYY/MM/DD HH:mm:ss` 形式でフォーマットする</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>CSV escape：値に `,`、`"`、改行を含む場合はダブルクォートで囲み `"` は `""` にエスケープする</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
+    <row r="99" ht="36" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>CSV escape：全ての値を無条件でダブルクォートで囲み、値中の `"` は `""` にエスケープする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="216" customHeight="1">
-      <c r="C95" s="42" t="inlineStr">
+    <row r="101" ht="216" customHeight="1">
+      <c r="C101" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9512,43 +9725,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D95" s="10" t="n"/>
-      <c r="E95" s="10" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="10" t="n"/>
-      <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="n"/>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="10" t="n"/>
-      <c r="M95" s="10" t="n"/>
-      <c r="N95" s="10" t="n"/>
-      <c r="O95" s="10" t="n"/>
-      <c r="P95" s="10" t="n"/>
-      <c r="Q95" s="10" t="n"/>
-      <c r="R95" s="10" t="n"/>
-      <c r="S95" s="10" t="n"/>
-      <c r="T95" s="10" t="n"/>
-      <c r="U95" s="10" t="n"/>
-      <c r="V95" s="10" t="n"/>
-      <c r="W95" s="10" t="n"/>
-      <c r="X95" s="10" t="n"/>
-      <c r="Y95" s="10" t="n"/>
-      <c r="Z95" s="10" t="n"/>
-      <c r="AA95" s="10" t="n"/>
-      <c r="AB95" s="10" t="n"/>
-      <c r="AC95" s="10" t="n"/>
-      <c r="AD95" s="10" t="n"/>
-      <c r="AE95" s="10" t="n"/>
-      <c r="AF95" s="10" t="n"/>
-      <c r="AG95" s="10" t="n"/>
-      <c r="AH95" s="10" t="n"/>
-      <c r="AI95" s="10" t="n"/>
-      <c r="AJ95" s="10" t="n"/>
-      <c r="AK95" s="11" t="n"/>
-    </row>
-    <row r="96" ht="180" customHeight="1">
-      <c r="C96" s="42" t="inlineStr">
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="10" t="n"/>
+      <c r="J101" s="10" t="n"/>
+      <c r="K101" s="10" t="n"/>
+      <c r="L101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
+      <c r="U101" s="10" t="n"/>
+      <c r="V101" s="10" t="n"/>
+      <c r="W101" s="10" t="n"/>
+      <c r="X101" s="10" t="n"/>
+      <c r="Y101" s="10" t="n"/>
+      <c r="Z101" s="10" t="n"/>
+      <c r="AA101" s="10" t="n"/>
+      <c r="AB101" s="10" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="10" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="10" t="n"/>
+      <c r="AK101" s="11" t="n"/>
+    </row>
+    <row r="102" ht="180" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>`before_value`：EXPORT のため空文字列を設定する。
 `after_value`：エクスポート条件と件数をJSON形式で格納する。
@@ -9561,92 +9774,92 @@
 }</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>CSV ファイルをレスポンスボディとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
         <is>
           <t>`Content-Type: text/csv; charset=utf-8`</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="36" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
+    <row r="106" ht="36" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
         <is>
           <t>`Content-Disposition: attachment; filename="log_export_YYYYMMDD_HHmmss.csv"`</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="C102" s="41" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="C103" s="41" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="216" customHeight="1">
-      <c r="C104" s="42" t="inlineStr">
+    <row r="110" ht="216" customHeight="1">
+      <c r="C110" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9662,43 +9875,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
-      <c r="P104" s="10" t="n"/>
-      <c r="Q104" s="10" t="n"/>
-      <c r="R104" s="10" t="n"/>
-      <c r="S104" s="10" t="n"/>
-      <c r="T104" s="10" t="n"/>
-      <c r="U104" s="10" t="n"/>
-      <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
-      <c r="X104" s="10" t="n"/>
-      <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" s="10" t="n"/>
-      <c r="AB104" s="10" t="n"/>
-      <c r="AC104" s="10" t="n"/>
-      <c r="AD104" s="10" t="n"/>
-      <c r="AE104" s="10" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
-      <c r="AI104" s="10" t="n"/>
-      <c r="AJ104" s="10" t="n"/>
-      <c r="AK104" s="11" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="10" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="10" t="n"/>
+      <c r="Y110" s="10" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="228">
+  <mergeCells count="232">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -9708,36 +9921,35 @@
     <mergeCell ref="B62:I62"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
-    <mergeCell ref="D71:AK71"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="B56:I56"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D73:AK73"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="C85:AK85"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
@@ -9746,11 +9958,14 @@
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="C51:AK51"/>
     <mergeCell ref="C95:AK95"/>
+    <mergeCell ref="B68:I68"/>
     <mergeCell ref="C22:L22"/>
+    <mergeCell ref="D77:AK77"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
@@ -9758,30 +9973,30 @@
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="C48:AK48"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="D75:AK75"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="B47:I47"/>
-    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="A32:AK32"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="B59:I59"/>
-    <mergeCell ref="B86:AK86"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="B67:AK67"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -9789,9 +10004,9 @@
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C99:AK99"/>
@@ -9806,10 +10021,9 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A66:AK66"/>
+    <mergeCell ref="D76:AK76"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="M27:P27"/>
@@ -9823,7 +10037,6 @@
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="C87:AK87"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
@@ -9837,6 +10050,7 @@
     <mergeCell ref="C98:AK98"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="A72:AK72"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -9848,7 +10062,6 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
     <mergeCell ref="AF40:AK40"/>
@@ -9856,6 +10069,7 @@
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
@@ -9868,7 +10082,7 @@
     <mergeCell ref="D80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="B94:AK94"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="M40:P40"/>
@@ -9888,41 +10102,44 @@
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="D74:AK74"/>
+    <mergeCell ref="B107:AK107"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B88:AK88"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="B53:I53"/>
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="B76:AK76"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="D86:AK86"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
@@ -9938,7 +10155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AK90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -10099,7 +10316,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10107,7 +10324,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -10223,7 +10440,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>アカウントプルダウンリストを取得する（DataScopeを呼び出しユーザーのロールに基づき自動適用。共用API）</t>
+          <t>アカウントプルダウンリストを取得する（キーワード検索＋ページング対応の無限スクロール用。DataScopeを呼び出しユーザーのロールに基づき自動適用。共用API）</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -10407,7 +10624,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>クエリパラメータ</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
@@ -10536,14 +10753,14 @@
       <c r="B15" s="35" t="n"/>
       <c r="I15" s="36" t="n"/>
       <c r="J15" s="17" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください</t>
+          <t>入力値が不正です</t>
         </is>
       </c>
       <c r="O15" s="10" t="n"/>
@@ -10574,14 +10791,14 @@
       <c r="B16" s="35" t="n"/>
       <c r="I16" s="36" t="n"/>
       <c r="J16" s="17" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K16" s="10" t="n"/>
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません</t>
+          <t>セッションが切れました。再度ログインしてください</t>
         </is>
       </c>
       <c r="O16" s="10" t="n"/>
@@ -10731,24 +10948,195 @@
       <c r="AJ21" s="10" t="n"/>
       <c r="AK21" s="11" t="n"/>
     </row>
-    <row r="22" ht="19.5" customHeight="1"/>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1"/>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="22" ht="36" customHeight="1">
+      <c r="B22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="11" t="n"/>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="11" t="n"/>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="11" t="n"/>
+      <c r="Y22" s="17" t="inlineStr"/>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="11" t="n"/>
+      <c r="AC22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="19" t="inlineStr">
+        <is>
+          <t>検索キーワード（部分一致・ILIKE）。`match_field` により対象カラムが変わる</t>
+        </is>
+      </c>
+      <c r="AG22" s="10" t="n"/>
+      <c r="AH22" s="10" t="n"/>
+      <c r="AI22" s="10" t="n"/>
+      <c r="AJ22" s="10" t="n"/>
+      <c r="AK22" s="11" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>match_field</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="11" t="n"/>
+      <c r="Y23" s="17" t="inlineStr"/>
+      <c r="Z23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="17" t="inlineStr"/>
+      <c r="AD23" s="10" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>検索対象フィールド（`both`：login_id OR account_name（既定）／`name`：account_nameのみ）。本画面の「ユーザー名」セレクトボックスは `name` を指定する</t>
+        </is>
+      </c>
+      <c r="AG23" s="10" t="n"/>
+      <c r="AH23" s="10" t="n"/>
+      <c r="AI23" s="10" t="n"/>
+      <c r="AJ23" s="10" t="n"/>
+      <c r="AK23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（デフォルト: 1、無限スクロールの読み込みページ）</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -10760,44 +11148,40 @@
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="11" t="n"/>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
         </is>
       </c>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R25" s="10" t="n"/>
       <c r="S25" s="11" t="n"/>
-      <c r="T25" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U25" s="10" t="n"/>
       <c r="V25" s="10" t="n"/>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
+      <c r="Y25" s="17" t="inlineStr"/>
       <c r="Z25" s="10" t="n"/>
       <c r="AA25" s="10" t="n"/>
-      <c r="AB25" s="10" t="n"/>
-      <c r="AC25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
-      <c r="AF25" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（デフォルト: 50、最大: 100）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -10806,13 +11190,13 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="B26" s="31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>include_id</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -10826,7 +11210,7 @@
       <c r="L26" s="11" t="n"/>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
@@ -10834,30 +11218,30 @@
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="10" t="n"/>
       <c r="S26" s="11" t="n"/>
-      <c r="T26" s="17" t="inlineStr"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U26" s="10" t="n"/>
       <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y26" s="17" t="inlineStr"/>
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
-      <c r="AB26" s="10" t="n"/>
-      <c r="AC26" s="10" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="17" t="inlineStr"/>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>アカウント一覧</t>
+          <t>編集フォーム用の退避パラメータ。指定した account_id がページ1のヒット範囲に含まれない場合、レスポンス先頭に追加して返す</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -10866,196 +11250,27 @@
       <c r="AJ26" s="10" t="n"/>
       <c r="AK26" s="11" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="37" t="n"/>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>account_id</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R27" s="10" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="17" t="inlineStr"/>
-      <c r="U27" s="10" t="n"/>
-      <c r="V27" s="10" t="n"/>
-      <c r="W27" s="10" t="n"/>
-      <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z27" s="10" t="n"/>
-      <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="10" t="n"/>
-      <c r="AC27" s="10" t="n"/>
-      <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="19" t="inlineStr">
-        <is>
-          <t>アカウントID</t>
-        </is>
-      </c>
-      <c r="AG27" s="10" t="n"/>
-      <c r="AH27" s="10" t="n"/>
-      <c r="AI27" s="10" t="n"/>
-      <c r="AJ27" s="10" t="n"/>
-      <c r="AK27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>login_id</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="n"/>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R28" s="10" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="17" t="inlineStr"/>
-      <c r="U28" s="10" t="n"/>
-      <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z28" s="10" t="n"/>
-      <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
-      <c r="AC28" s="10" t="n"/>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="11" t="n"/>
-      <c r="AF28" s="19" t="inlineStr">
-        <is>
-          <t>ログインID</t>
-        </is>
-      </c>
-      <c r="AG28" s="10" t="n"/>
-      <c r="AH28" s="10" t="n"/>
-      <c r="AI28" s="10" t="n"/>
-      <c r="AJ28" s="10" t="n"/>
-      <c r="AK28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>account_name</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="17" t="inlineStr"/>
-      <c r="U29" s="10" t="n"/>
-      <c r="V29" s="10" t="n"/>
-      <c r="W29" s="10" t="n"/>
-      <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z29" s="10" t="n"/>
-      <c r="AA29" s="10" t="n"/>
-      <c r="AB29" s="10" t="n"/>
-      <c r="AC29" s="10" t="n"/>
-      <c r="AD29" s="10" t="n"/>
-      <c r="AE29" s="11" t="n"/>
-      <c r="AF29" s="19" t="inlineStr">
-        <is>
-          <t>アカウント名</t>
-        </is>
-      </c>
-      <c r="AG29" s="10" t="n"/>
-      <c r="AH29" s="10" t="n"/>
-      <c r="AI29" s="10" t="n"/>
-      <c r="AJ29" s="10" t="n"/>
-      <c r="AK29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>role_code</t>
-        </is>
-      </c>
+    <row r="27" ht="19.5" customHeight="1"/>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
@@ -11064,29 +11279,33 @@
       <c r="J30" s="10" t="n"/>
       <c r="K30" s="10" t="n"/>
       <c r="L30" s="11" t="n"/>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q30" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="11" t="n"/>
-      <c r="T30" s="17" t="inlineStr"/>
+      <c r="T30" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y30" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z30" s="10" t="n"/>
@@ -11095,9 +11314,9 @@
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
-      <c r="AF30" s="19" t="inlineStr">
-        <is>
-          <t>ロールコード</t>
+      <c r="AF30" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -11108,14 +11327,14 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
@@ -11126,7 +11345,7 @@
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N31" s="10" t="n"/>
@@ -11134,7 +11353,7 @@
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R31" s="10" t="n"/>
@@ -11146,7 +11365,7 @@
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z31" s="10" t="n"/>
@@ -11157,7 +11376,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>アカウント一覧</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -11166,21 +11385,136 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="B33" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>アカウントID</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>login_id</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="17" t="inlineStr"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="10" t="n"/>
+      <c r="AC33" s="10" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="19" t="inlineStr">
+        <is>
+          <t>ログインID</t>
+        </is>
+      </c>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="11" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/account/dropdown</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
+      <c r="B34" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>account_name</t>
+        </is>
+      </c>
       <c r="E34" s="10" t="n"/>
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
@@ -11188,42 +11522,527 @@
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n"/>
-      <c r="Q34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R34" s="10" t="n"/>
-      <c r="S34" s="10" t="n"/>
-      <c r="T34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
-      <c r="X34" s="10" t="n"/>
-      <c r="Y34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z34" s="10" t="n"/>
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="10" t="n"/>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="10" t="n"/>
-      <c r="AF34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>アカウント名</t>
+        </is>
+      </c>
       <c r="AG34" s="10" t="n"/>
       <c r="AH34" s="10" t="n"/>
       <c r="AI34" s="10" t="n"/>
       <c r="AJ34" s="10" t="n"/>
       <c r="AK34" s="11" t="n"/>
     </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="B36" s="40" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>role_code</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="17" t="inlineStr"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="19" t="inlineStr">
+        <is>
+          <t>ロールコード</t>
+        </is>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>ja_id</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="17" t="inlineStr"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="11" t="n"/>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>JA ID</t>
+        </is>
+      </c>
+      <c r="AG36" s="10" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="10" t="n"/>
+      <c r="AJ36" s="10" t="n"/>
+      <c r="AK36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="17" t="inlineStr"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="19" t="inlineStr">
+        <is>
+          <t>ページネーション情報</t>
+        </is>
+      </c>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="17" t="inlineStr"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="19" t="inlineStr">
+        <is>
+          <t>検索条件（q / match_field）適用後の総件数</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="17" t="inlineStr"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="11" t="n"/>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="19" t="inlineStr">
+        <is>
+          <t>現在ページ番号</t>
+        </is>
+      </c>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="17" t="inlineStr"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="11" t="n"/>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="B41" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>has_more</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="17" t="inlineStr"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="19" t="inlineStr">
+        <is>
+          <t>次ページが存在するか（`page * per_page &lt; total`）。無限スクロールの追加読込判定に使用</t>
+        </is>
+      </c>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1"/>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/account/dropdown?match_field=name&amp;q=%E5%A4%AA%E9%83%8E&amp;page=1&amp;per_page=50</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="324" customHeight="1">
-      <c r="C37" s="19" t="inlineStr">
+    <row r="47" ht="409" customHeight="1">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -11241,54 +12060,60 @@
       "role_code": "JA_KANRI_SHITEN",
       "ja_id": 100
     }
-  ]
+  ],
+  "meta": {
+    "total": 2,
+    "page": 1,
+    "per_page": 50,
+    "has_more": false
+  }
 }</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="B39" s="40" t="inlineStr">
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="72" customHeight="1">
-      <c r="C40" s="19" t="inlineStr">
+    <row r="50" ht="72" customHeight="1">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -11296,101 +12121,104 @@
 }</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="11" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="B42" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="C43" s="19" t="inlineStr">
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Validation Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="126" customHeight="1">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [
+    { "field": "match_field", "message": "match_fieldは\"both\"または\"name\"で指定してください。" }
+  ]
 }</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="10" t="n"/>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="11" t="n"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AF53" s="10" t="n"/>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
+    <row r="56" ht="72" customHeight="1">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -11398,156 +12226,233 @@
 }</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1"/>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="10" t="n"/>
+      <c r="AF56" s="10" t="n"/>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1"/>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="27" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="C51" s="41" t="inlineStr">
-        <is>
-          <t>リクエストパラメータなし。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="C53" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：認証済みユーザーであればアクセス可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>※ 呼び出し元画面の権限に依存する。SCR-030（ログ参照画面）では `log.view` 保持者が呼び出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>DataScope を role_code により適用する：</t>
-        </is>
-      </c>
-    </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="D61" s="41" t="inlineStr">
-        <is>
-          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全アカウントを取得</t>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="D62" s="41" t="inlineStr">
         <is>
-          <t>`CHUOKAI`：`a.ja_id = :user_ja_id`</t>
+          <t>q：文字列、最大100文字（空文字は未指定として扱う）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="D63" s="41" t="inlineStr">
         <is>
+          <t>match_field：`both` または `name`（未指定時は `both`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>page：整数、1以上（未指定時は1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>per_page：整数、1〜100（未指定時は50）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="D66" s="41" t="inlineStr">
+        <is>
+          <t>include_id：整数、1以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：本エンドポイントには `@Permissions` が付与されていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>※ 呼び出し元画面ごとの権限は各画面の permission gate（例：SCR-030 ログ参照画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープ（role_code, ja_id, kanri_shiten_id）を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>DataScope を role_code により適用する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="D76" s="41" t="inlineStr">
+        <is>
+          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`：全アカウントを取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>`CHUOKAI`：`a.ja_id = :user_ja_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="D78" s="41" t="inlineStr">
+        <is>
           <t>`JA_HONTEN`：`a.ja_id = :user_ja_id`</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="36" customHeight="1">
-      <c r="D64" s="41" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
         <is>
           <t>`JA_KANRI_SHITEN`：`a.kanri_shiten_id = :user_kanri_shiten_id`</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="180" customHeight="1">
-      <c r="C65" s="42" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>検索条件（q）を追加する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>`match_field = 'name'`：`a.account_name ILIKE :q`</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>`match_field` 未指定 または `both`：`a.login_id ILIKE :q OR a.account_name ILIKE :q`</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>ページング：`ORDER BY a.login_id ASC` の上で `LIMIT :per_page OFFSET (:page - 1) * :per_page`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>`include_id` 指定時、その account_id が現在ページの結果に含まれなければ、同一</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>総件数（total）は同一 DataScope・検索条件で `COUNT(*)` を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="270" customHeight="1">
+      <c r="C86" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name,
        r.role_code, a.ja_id
@@ -11558,195 +12463,277 @@
   AND a.ja_id = :user_ja_id
   /* DataScope: JA_KANRI_SHITEN */
   AND a.kanri_shiten_id = :user_kanri_shiten_id
-ORDER BY a.login_id ASC</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n"/>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n"/>
-      <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
-      <c r="T65" s="10" t="n"/>
-      <c r="U65" s="10" t="n"/>
-      <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n"/>
-      <c r="X65" s="10" t="n"/>
-      <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
-      <c r="AA65" s="10" t="n"/>
-      <c r="AB65" s="10" t="n"/>
-      <c r="AC65" s="10" t="n"/>
-      <c r="AD65" s="10" t="n"/>
-      <c r="AE65" s="10" t="n"/>
-      <c r="AF65" s="10" t="n"/>
-      <c r="AG65" s="10" t="n"/>
-      <c r="AH65" s="10" t="n"/>
-      <c r="AI65" s="10" t="n"/>
-      <c r="AJ65" s="10" t="n"/>
-      <c r="AK65" s="11" t="n"/>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
+  /* 検索条件: match_field='name' */
+  AND a.account_name ILIKE :q
+  /* 検索条件: match_field='both'（既定） */
+  AND (a.login_id ILIKE :q OR a.account_name ILIKE :q)
+ORDER BY a.login_id ASC
+LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="10" t="n"/>
+      <c r="J86" s="10" t="n"/>
+      <c r="K86" s="10" t="n"/>
+      <c r="L86" s="10" t="n"/>
+      <c r="M86" s="10" t="n"/>
+      <c r="N86" s="10" t="n"/>
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="10" t="n"/>
+      <c r="S86" s="10" t="n"/>
+      <c r="T86" s="10" t="n"/>
+      <c r="U86" s="10" t="n"/>
+      <c r="V86" s="10" t="n"/>
+      <c r="W86" s="10" t="n"/>
+      <c r="X86" s="10" t="n"/>
+      <c r="Y86" s="10" t="n"/>
+      <c r="Z86" s="10" t="n"/>
+      <c r="AA86" s="10" t="n"/>
+      <c r="AB86" s="10" t="n"/>
+      <c r="AC86" s="10" t="n"/>
+      <c r="AD86" s="10" t="n"/>
+      <c r="AE86" s="10" t="n"/>
+      <c r="AF86" s="10" t="n"/>
+      <c r="AG86" s="10" t="n"/>
+      <c r="AH86" s="10" t="n"/>
+      <c r="AI86" s="10" t="n"/>
+      <c r="AJ86" s="10" t="n"/>
+      <c r="AK86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>data 配列を含むJSONを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
+    <row r="88" ht="36" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta（total, page, per_page, has_more）を含むJSONを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="41" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="198">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y27:AE27"/>
-    <mergeCell ref="C57:AK57"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="D78:AK78"/>
+    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="T33:X33"/>
+    <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C53:AK53"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="C34:AK34"/>
-    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="M23:P23"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="D64:AK64"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="D82:AK82"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="B73:AK73"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="A49:AK49"/>
+    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="C46:AK46"/>
+    <mergeCell ref="D35:L35"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="C51:AK51"/>
-    <mergeCell ref="B50:AK50"/>
-    <mergeCell ref="Y26:AE26"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="D77:AK77"/>
+    <mergeCell ref="T34:X34"/>
     <mergeCell ref="M25:P25"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="D61:AK61"/>
-    <mergeCell ref="B66:AK66"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="M33:P33"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="A23:AK23"/>
     <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D56:AK56"/>
+    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="B89:AK89"/>
+    <mergeCell ref="D65:AK65"/>
+    <mergeCell ref="B49:I49"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="Y28:AE28"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="C37:AK37"/>
-    <mergeCell ref="D27:L27"/>
-    <mergeCell ref="B58:AK58"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="D76:AK76"/>
+    <mergeCell ref="D66:AK66"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="T39:X39"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B52:AK52"/>
-    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T32:X32"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="B60:AK60"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C37:L37"/>
+    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="D28:L28"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="M34:P34"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C54:AK54"/>
-    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T21:X21"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C50:AK50"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="C43:AK43"/>
+    <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="C38:C41"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
-    <mergeCell ref="Y25:AE25"/>
-    <mergeCell ref="T27:X27"/>
+    <mergeCell ref="T36:X36"/>
     <mergeCell ref="B14:I17"/>
+    <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="D32:L32"/>
     <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q40:S40"/>
     <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="A19:AK19"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="A28:AK28"/>
+    <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="A59:AK59"/>
     <mergeCell ref="B68:AK68"/>
-    <mergeCell ref="C40:AK40"/>
-    <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="D31:L31"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M37:P37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
